--- a/Buffet - SENAC/Páginas_Buffet.xlsx
+++ b/Buffet - SENAC/Páginas_Buffet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\07228257146\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\07228257146\Oracle_apex\Buffet - SENAC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D26D4B-7C87-4C54-9FFE-EEF7A0E692CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37280B68-4BFA-490F-BF69-E9087BA14A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{958EFF2B-B475-465C-8BB6-E53DB46936BF}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{958EFF2B-B475-465C-8BB6-E53DB46936BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -475,6 +475,9 @@
       <c r="E3">
         <v>500</v>
       </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
       <c r="G3">
         <v>870</v>
       </c>
@@ -495,6 +498,9 @@
       <c r="E4">
         <v>570</v>
       </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
       <c r="G4">
         <v>871</v>
       </c>
@@ -515,6 +521,9 @@
       <c r="E5">
         <v>571</v>
       </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
       <c r="G5">
         <v>900</v>
       </c>
@@ -538,6 +547,9 @@
       <c r="E6">
         <v>600</v>
       </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
       <c r="G6">
         <v>1000</v>
       </c>
@@ -558,6 +570,9 @@
       <c r="E7">
         <v>601</v>
       </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
       <c r="G7">
         <v>1070</v>
       </c>
@@ -578,6 +593,9 @@
       <c r="E8">
         <v>602</v>
       </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
       <c r="G8">
         <v>1071</v>
       </c>
@@ -598,6 +616,9 @@
       <c r="E9">
         <v>603</v>
       </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
       <c r="G9">
         <v>1100</v>
       </c>
@@ -618,8 +639,14 @@
       <c r="E10">
         <v>670</v>
       </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
       <c r="G10">
         <v>1200</v>
+      </c>
+      <c r="H10">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -638,8 +665,14 @@
       <c r="E11">
         <v>671</v>
       </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
       <c r="G11">
         <v>1270</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -658,8 +691,14 @@
       <c r="E12">
         <v>672</v>
       </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
       <c r="G12">
         <v>1271</v>
+      </c>
+      <c r="H12">
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -676,6 +715,9 @@
       <c r="E13">
         <v>673</v>
       </c>
+      <c r="F13">
+        <v>7</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -692,6 +734,9 @@
       </c>
       <c r="E14">
         <v>674</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">

--- a/Buffet - SENAC/Páginas_Buffet.xlsx
+++ b/Buffet - SENAC/Páginas_Buffet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\07228257146\Oracle_apex\Buffet - SENAC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\07228257146\Oracle_apex\Buffet - SENAC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37280B68-4BFA-490F-BF69-E9087BA14A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0248A4F2-F3BB-485B-9268-55DA2FD034BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{958EFF2B-B475-465C-8BB6-E53DB46936BF}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="16200" windowHeight="9270" xr2:uid="{958EFF2B-B475-465C-8BB6-E53DB46936BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -458,6 +458,9 @@
       <c r="G2">
         <v>800</v>
       </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -481,6 +484,9 @@
       <c r="G3">
         <v>870</v>
       </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -504,6 +510,9 @@
       <c r="G4">
         <v>871</v>
       </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -553,6 +562,9 @@
       <c r="G6">
         <v>1000</v>
       </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -576,6 +588,9 @@
       <c r="G7">
         <v>1070</v>
       </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -599,6 +614,9 @@
       <c r="G8">
         <v>1071</v>
       </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -622,6 +640,9 @@
       <c r="G9">
         <v>1100</v>
       </c>
+      <c r="H9">
+        <v>11</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -752,8 +773,11 @@
       <c r="D15">
         <v>3</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>700</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">

--- a/Buffet - SENAC/Páginas_Buffet.xlsx
+++ b/Buffet - SENAC/Páginas_Buffet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\07228257146\Oracle_apex\Buffet - SENAC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tchel\Oracle_apex\Buffet - SENAC\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0248A4F2-F3BB-485B-9268-55DA2FD034BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="16200" windowHeight="9270" xr2:uid="{958EFF2B-B475-465C-8BB6-E53DB46936BF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{958EFF2B-B475-465C-8BB6-E53DB46936BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -420,9 +420,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79399E5A-7257-49A0-8C7B-8EB54A5EB783}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>0</v>
       </c>
@@ -436,7 +436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -462,7 +462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>100</v>
       </c>
@@ -488,7 +488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>170</v>
       </c>
@@ -514,7 +514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>171</v>
       </c>
@@ -540,7 +540,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>200</v>
       </c>
@@ -566,7 +566,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>201</v>
       </c>
@@ -592,7 +592,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>202</v>
       </c>
@@ -618,7 +618,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>203</v>
       </c>
@@ -644,7 +644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>204</v>
       </c>
@@ -670,7 +670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>270</v>
       </c>
@@ -696,7 +696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>271</v>
       </c>
@@ -722,7 +722,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>274</v>
       </c>
@@ -740,7 +740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>275</v>
       </c>
@@ -760,7 +760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>276</v>
       </c>
@@ -780,7 +780,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>277</v>
       </c>
